--- a/data_extactor/batch_10_fa/trimmed/batch_0007_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0007_fa_trim.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>سخن گفتن | تفکر انتقادی | شنیدن فعال | درک مطلب | نگارش | یادگیری فعال | نظارت | ریاضیات</t>
+          <t>سخن گفتن | تفکر انتقادی | گوش دادن فعال | درک مطلب | نگارش | یادگیری فعال | نظارت | ریاضیات</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ریاضیات | خدمات مشتریان و خدمات فردی | حمل‌ونقل | اقتصاد و حسابداری | فروش و بازاریابی | تولید مواد غذایی | تولید و فرآوری</t>
+          <t>ریاضیات | خدمات مشتری و شخصی | حمل و نقل | اقتصاد و حسابداری | فروش و بازاریابی | تولید مواد غذایی | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | کار با اعداد</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | توانایی عددی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>بازرسان کشاورزی | کشاورزان، دامداران و سایر مدیران کشاورزی | کارشناسان لجستیک | کارمندان تدارکات | کارشناسان خرید و امور قراردادها | مدیران خرید | خریداران عمده‌فروشی و خرده‌فروشی کالاهای غیرکشاورزی</t>
+          <t>بازرسان محصولات و فرآورده‌های کشاورزی | مدیران امور کشاورزی، دامپروری و شیلات | کارشناسان لجستیک و مدیریت زنجیره تأمین | کارمندان تدارکات و کارپردازی | کارشناسان خرید و امور قراردادها | مدیران خرید و تدارکات | خریداران عمده‌فروشی و خرده‌فروشی کالاهای غیرکشاورزی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | سخن گفتن | یادگیری فعال | درک مطلب | ریاضیات | نظارت | نگارش</t>
+          <t>تفکر انتقادی | گوش دادن فعال | سخن گفتن | یادگیری فعال | درک مطلب | ریاضیات | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>فروش و بازاریابی | خدمات مشتریان و خدمات فردی | زبان انگلیسی | ریاضیات | مدیریت و امور اداری | رایانه و الکترونیک | اقتصاد و حسابداری</t>
+          <t>فروش و بازاریابی | خدمات مشتری و شخصی | زبان انگلیسی | ریاضیات | مدیریت و اداره | رایانه و الکترونیک | اقتصاد و حسابداری</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | استدلال قیاسی | درک کتبی | حساسیت به مسئله | استدلال ریاضی | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | بیان شفاهی | استدلال قیاسی | درک کتبی | حساسیت به مسئله | استدلال ریاضی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>خریداران و کارشناسان خرید محصولات کشاورزی | فروشندگان اینترنتی | کارمندان تدارکات | کارشناسان خرید و امور قراردادها | مدیران خرید | فروشندگان خرده‌فروشی | نمایندگان فروش عمده‌فروشی و تولیدی محصولات غیرفنی و غیرعلمی</t>
+          <t>خریداران و کارشناسان خرید محصولات کشاورزی | کارشناسان تجارت الکترونیک و فروشگاه‌های اینترنتی | کارمندان تدارکات و کارپردازی | کارشناسان خرید و امور قراردادها | مدیران خرید و تدارکات | فروشندگان خرده‌فروشی | کارشناسان فروش عمده و سازمانی محصولات غیرفنی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>درک مطلب | سخن گفتن | نگارش | شنیدن فعال | تفکر انتقادی | یادگیری فعال | نظارت | استراتژی‌های یادگیری | ریاضیات</t>
+          <t>درک مطلب | سخن گفتن | نگارش | گوش دادن فعال | تفکر انتقادی | یادگیری فعال | نظارت | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>حقوق و مقررات دولتی | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | امور اداری و دفتری | ریاضیات | رایانه و الکترونیک | اقتصاد و حسابداری</t>
+          <t>قانون و دولت | خدمات مشتری و شخصی | مدیریت و اداره | اداری | ریاضیات | رایانه و الکترونیک | اقتصاد و حسابداری</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک کتبی | درک شفاهی | بیان شفاهی | بیان کتبی | استدلال قیاسی | مرتب‌سازی اطلاعات | حساسیت به مسئله</t>
+          <t>درک کتبی | درک شفاهی | بیان شفاهی | بیان کتبی | استدلال قیاسی | ترتیب‌دهی اطلاعات | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>برآوردکنندگان هزینه | کارگزاران گمرکی | کارشناسان لجستیک | کارمندان تدارکات | مدیران خرید | مدیران زنجیره تأمین | خریداران عمده‌فروشی و خرده‌فروشی کالاهای غیرکشاورزی</t>
+          <t>کارشناسان برآورد هزینه و مترورها | حق‌العمل‌کاران و کارگزاران گمرکی | کارشناسان لجستیک و مدیریت زنجیره تأمین | کارمندان تدارکات و کارپردازی | مدیران خرید و تدارکات | مدیران زنجیره تامین | خریداران عمده‌فروشی و خرده‌فروشی کالاهای غیرکشاورزی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,12 +679,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | امور اداری و دفتری | ریاضیات | رایانه و الکترونیک | حقوق و مقررات دولتی | مدیریت و امور اداری | اقتصاد و حسابداری</t>
+          <t>خدمات مشتری و شخصی | اداری | ریاضیات | رایانه و الکترونیک | قانون و دولت | مدیریت و اداره | اقتصاد و حسابداری</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ارزیابان و کارشناسان املاک و مستغلات | کارشناسان اعتبارسنجی و تأیید اسناد مالی | کارشناسان و بازرسان بررسی تقلب‌های مالیاتی و تخلفات | کارمندان صدور و پرداخت خسارت بیمه | نمایندگان فروش بیمه | کارشناسان ارزیابی ریسک بیمه (آندرایتر) | کارآگاهان و بازرسان خصوصی</t>
+          <t>کارشناسان ارزیابی و ممیزی املاک و مستغلات | کارشناسان اعتبارسنجی، بررسی و تایید تسهیلات | کارشناسان بازرسی، کشف و تحلیل تقلب | کارمندان پردازش خسارت و بیمه‌نامه‌ها | نمایندگان و کارشناسان فروش بیمه | کارشناسان صدور بیمه‌نامه و ارزیابی ریسک | کارآگاهان و بازرسان خصوصی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>نگارش | سخن گفتن | درک مطلب | شنیدن فعال | تفکر انتقادی</t>
+          <t>نگارش | سخن گفتن | درک مطلب | گوش دادن فعال | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | رایانه و الکترونیک | مکانیک | امور اداری و دفتری</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | رایانه و الکترونیک | مکانیک | اداری</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک کتبی | حساسیت به مسئله | بیان کتبی | دید نزدیک | استدلال قیاسی</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | حساسیت به مسئله | بیان کتبی | بینایی نزدیک | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>صافکاران و تعمیرکاران بدنه خودرو | تکنسین‌های مهندسی خودرو | تکنسین‌ها و مکانیک‌های خدمات پس از فروش خودرو | کارشناسان ارزیابی و رسیدگی به خسارت‌های بیمه‌ای | برآوردکنندگان هزینه | کارمندان صدور و پرداخت خسارت بیمه | فروشندگان لوازم یدکی خودرو</t>
+          <t>صافکار و نقاش خودرو | تکنسین‌های مهندسی خودرو | مکانیک و تکنسین خدمات خودرو | کارشناسان ارزیابی و رسیدگی به خسارت‌های بیمه‌ای | کارشناسان برآورد هزینه و مترورها | کارمندان پردازش خسارت و بیمه‌نامه‌ها | فروشندگان قطعات و لوازم یدکی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب | سخن گفتن | شنیدن فعال | نگارش | تفکر انتقادی | نظارت | یادگیری فعال</t>
+          <t>درک مطلب | سخن گفتن | گوش دادن فعال | نگارش | تفکر انتقادی | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>حقوق و مقررات دولتی | زبان انگلیسی | خدمات مشتریان و خدمات فردی | ایمنی و امنیت عمومی | رایانه و الکترونیک | مدیریت و امور اداری | امور اداری و دفتری</t>
+          <t>قانون و دولت | زبان انگلیسی | خدمات مشتری و شخصی | ایمنی و امنیت عمومی | رایانه و الکترونیک | مدیریت و اداره | اداری</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | حساسیت به مسئله | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | حساسیت به مسئله | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مدیران امور انطباق و بازرسی | کارمندان دادگاه‌ها، شهرداری‌ها و مراجع صدور پروانه | بازرسان رعایت ضوابط زیست‌محیطی | بازرسان و ممیزان اموال دولتی | کارشناسان حقوقی و دستیاران وکالت | کارشناسان امور نظارتی و تطبیق مقررات | ممیزان، بازرسان و مأموران وصول مالیات</t>
+          <t>مدیران تطبیق و نظارت مقرراتی | کارمندان و متصدیان امور دفتری دادگاه‌ها، شهرداری‌ها و مراجع صدور پروانه | بازرسان رعایت ضوابط زیست‌محیطی | بازرسان و ممیزان اموال دولتی | کارشناسان و دستیاران امور حقوقی | کارشناسان امور رگولاتوری و انطباق مقرراتی | ممیزان، ماموران وصول و کارشناسان مالیاتی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,12 +850,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | شنیدن فعال | نگارش | سخن گفتن | یادگیری فعال | نظارت | استراتژی‌های یادگیری | علوم پایه | ریاضیات</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | نگارش | سخن گفتن | یادگیری فعال | نظارت | راهبردهای یادگیری | علوم | ریاضیات</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | حقوق و مقررات دولتی | رایانه و الکترونیک | شیمی | خدمات مشتریان و خدمات فردی | ریاضیات | ایمنی و امنیت عمومی</t>
+          <t>زبان انگلیسی | قانون و دولت | رایانه و الکترونیک | شیمی | خدمات مشتری و شخصی | ریاضیات | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>مدیران امور انطباق و بازرسی | تکنسین‌ها و کاردان‌های فنی مهندسی محیط زیست | مهندسان محیط زیست | کارشناسان و دانشمندان علوم محیطی و بهداشت عمومی | مهندسان بهداشت حرفه‌ای و ایمنی کار (به‌جز معدن) | کارشناسان بهداشت حرفه‌ای و ایمنی محیط کار | کارشناسان امور نظارتی و تطبیق مقررات</t>
+          <t>مدیران تطبیق و نظارت مقرراتی | کارشناسان و تکنسین‌های مهندسی محیط زیست | مهندسان محیط‌زیست | کارشناسان و متخصصان علوم محیطی (شامل بهداشت) | مهندسان بهداشت و ایمنی، به‌جز مهندسان و بازرسان ایمنی معدن | کارشناسان بهداشت حرفه‌ای و ایمنی کار | کارشناسان امور رگولاتوری و انطباق مقرراتی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>شنیدن فعال | درک مطلب | تفکر انتقادی | سخن گفتن | نگارش | یادگیری فعال | نظارت | استراتژی‌های یادگیری</t>
+          <t>گوش دادن فعال | درک مطلب | تفکر انتقادی | سخن گفتن | نگارش | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>حقوق و مقررات دولتی | امور اداری و منابع انسانی | خدمات مشتریان و خدمات فردی | جامعه‌شناسی و مردم‌شناسی | مدیریت و امور اداری | امور اداری و دفتری</t>
+          <t>قانون و دولت | پرسنل و منابع انسانی | خدمات مشتری و شخصی | جامعه‌شناسی و انسان‌شناسی | مدیریت و اداره | اداری</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک کتبی | درک شفاهی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال استقرایی | مرتب‌سازی اطلاعات</t>
+          <t>درک کتبی | درک شفاهی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال استقرایی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>داوران، میانجی‌گران و صلح‌دهندگان | کارشناسان جبران خدمت، مزایا و طبقه‌بندی مشاغل | کارشناسان پایش انطباق و بازرسی مقرراتی | مدیران منابع انسانی | کارشناسان منابع انسانی | کارشناسان روابط کار | کارشناسان امور نظارتی و تطبیق مقررات</t>
+          <t>داوران، میانجی‌گران و صلح‌یاران | کارشناسان جبران خدمت، مزایا و طبقه‌بندی مشاغل | کارشناسان پایش انطباق و بازرسی مقرراتی | مدیران منابع انسانی | کارشناسان منابع انسانی | کارشناسان روابط کار و امور تشکل‌های کارگری | کارشناسان امور رگولاتوری و انطباق مقرراتی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | سخن گفتن | نگارش | درک مطلب | یادگیری فعال | نظارت | استراتژی‌های یادگیری</t>
+          <t>گوش دادن فعال | تفکر انتقادی | سخن گفتن | نگارش | درک مطلب | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | ساختمان و ساخت‌وساز | حقوق و مقررات دولتی | امور اداری و دفتری | مهندسی و فناوری | مکانیک</t>
+          <t>ایمنی و امنیت عمومی | ساختمان و ساخت‌وساز | قانون و دولت | اداری | مهندسی و فناوری | مکانیک</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>استدلال استقرایی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | مرتب‌سازی اطلاعات | درک شفاهی | درک کتبی</t>
+          <t>استدلال استقرایی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | ترتیب‌دهی اطلاعات | درک شفاهی | درک کتبی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>کاردان‌ها و تکنسین‌های فنی مهندسی عمران | مدیران امور انطباق و بازرسی | کارشناسان پایش انطباق و بازرسی مقرراتی | بازرسان ساختمان و ابنیه | بازرسان رعایت ضوابط زیست‌محیطی | کارشناسان بهداشت حرفه‌ای و ایمنی محیط کار | کارشناسان بررسی و جستجوی اسناد مالکیت</t>
+          <t>کارشناسان و تکنسین‌های مهندسی عمران | مدیران تطبیق و نظارت مقرراتی | کارشناسان پایش انطباق و بازرسی مقرراتی | بازرسان ساخت‌وساز و ساختمان | بازرسان رعایت ضوابط زیست‌محیطی | کارشناسان بهداشت حرفه‌ای و ایمنی کار | کارشناسان بررسی اسناد مالکیت و خلاصه‌برداری اسناد ثبتی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,12 +1021,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | درک مطلب | شنیدن فعال | نگارش | یادگیری فعال | نظارت | علوم پایه | استراتژی‌های یادگیری</t>
+          <t>تفکر انتقادی | سخن گفتن | درک مطلب | گوش دادن فعال | نگارش | یادگیری فعال | نظارت | علوم | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>پزشکی و دندان‌پزشکی | حقوق و مقررات دولتی | مدیریت و امور اداری | زیست‌شناسی | ایمنی و امنیت عمومی | روان‌شناسی</t>
+          <t>پزشکی و دندان‌پزشکی | قانون و دولت | مدیریت و اداره | زیست‌شناسی | ایمنی و امنیت عمومی | روان‌شناسی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>کارآگاهان و بازرسان جنایی | تکنسین‌های علوم آزمایشگاهی پزشکی قانونی | کارشناسان مدارک و اسناد پزشکی | پزشکان آسیب‌شناس (پاتولوژیست) | کارشناسان ثبت هویت و اسناد پلیس | پزشکان طب کار و پیشگیری</t>
+          <t>کارآگاهان و بازرسان جنایی | کاردان‌ها و تکنسین‌های علوم آزمایشگاهی و کشف علمی جرایم | کارشناسان و تکنسین‌های مدارک پزشکی و فناوری اطلاعات سلامت | پزشکان متخصص پاتولوژی | کارشناسان تشخیص هویت و ثبت سوابق پلیس | متخصصان پزشکی اجتماعی و طب پیشگیری</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
